--- a/diseases/d240/2015-2019.xlsx
+++ b/diseases/d240/2015-2019.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -18328,7 +18328,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -22641,7 +22641,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -25592,7 +25592,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -28316,7 +28316,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -29905,7 +29905,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -31267,7 +31267,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -32629,7 +32629,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -34218,7 +34218,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -35580,7 +35580,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -38531,7 +38531,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -39893,7 +39893,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -41255,7 +41255,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -42844,7 +42844,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -44206,7 +44206,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -45568,7 +45568,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -47157,7 +47157,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -48519,7 +48519,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -51470,7 +51470,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -52832,7 +52832,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -54194,7 +54194,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -55783,7 +55783,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -57145,7 +57145,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -58507,7 +58507,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -60096,7 +60096,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -61458,7 +61458,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -63047,7 +63047,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -64409,7 +64409,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -65771,7 +65771,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -67360,7 +67360,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -68722,7 +68722,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -70084,7 +70084,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -71673,7 +71673,7 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN314" t="b">
@@ -73035,7 +73035,7 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN320" t="b">
@@ -74397,7 +74397,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -75986,7 +75986,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -77348,7 +77348,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -78710,7 +78710,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN345" t="b">
@@ -80299,7 +80299,7 @@
       </c>
       <c r="AM352" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN352" t="b">
@@ -81661,7 +81661,7 @@
       </c>
       <c r="AM358" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN358" t="b">
@@ -83023,7 +83023,7 @@
       </c>
       <c r="AM364" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN364" t="b">

--- a/diseases/d240/2015-2019.xlsx
+++ b/diseases/d240/2015-2019.xlsx
@@ -849,7 +849,7 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN2" t="b">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -15377,7 +15377,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -18328,7 +18328,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -22641,7 +22641,7 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN98" t="b">
@@ -24003,7 +24003,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -25592,7 +25592,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -28316,7 +28316,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -29905,7 +29905,7 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN130" t="b">
@@ -31267,7 +31267,7 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN136" t="b">
@@ -32629,7 +32629,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -34218,7 +34218,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -35580,7 +35580,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -38531,7 +38531,7 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN168" t="b">
@@ -39893,7 +39893,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -41255,7 +41255,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -42844,7 +42844,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -44206,7 +44206,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -45568,7 +45568,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -47157,7 +47157,7 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN206" t="b">
@@ -48519,7 +48519,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -50108,7 +50108,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -51470,7 +51470,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -52832,7 +52832,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -54194,7 +54194,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -55783,7 +55783,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -57145,7 +57145,7 @@
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN250" t="b">
@@ -58507,7 +58507,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -60096,7 +60096,7 @@
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -61458,7 +61458,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -63047,7 +63047,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -64409,7 +64409,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -65771,7 +65771,7 @@
       </c>
       <c r="AM288" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN288" t="b">
@@ -67360,7 +67360,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -68722,7 +68722,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -70084,7 +70084,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -71673,7 +71673,7 @@
       </c>
       <c r="AM314" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN314" t="b">
@@ -73035,7 +73035,7 @@
       </c>
       <c r="AM320" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN320" t="b">
@@ -74397,7 +74397,7 @@
       </c>
       <c r="AM326" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN326" t="b">
@@ -75986,7 +75986,7 @@
       </c>
       <c r="AM333" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN333" t="b">
@@ -77348,7 +77348,7 @@
       </c>
       <c r="AM339" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN339" t="b">
@@ -78710,7 +78710,7 @@
       </c>
       <c r="AM345" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN345" t="b">
@@ -80299,7 +80299,7 @@
       </c>
       <c r="AM352" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN352" t="b">
@@ -81661,7 +81661,7 @@
       </c>
       <c r="AM358" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN358" t="b">
@@ -83023,7 +83023,7 @@
       </c>
       <c r="AM364" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN364" t="b">

--- a/diseases/d240/2015-2019.xlsx
+++ b/diseases/d240/2015-2019.xlsx
@@ -15471,7 +15471,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -15517,34 +15517,15 @@
       <c r="N67" t="n">
         <v>48</v>
       </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O67" t="n">
+        <v>48</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.4837110310300626</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -15552,86 +15533,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN67" t="b">
-        <v>0</v>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -17060,7 +16983,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -17106,34 +17029,15 @@
       <c r="N74" t="n">
         <v>29</v>
       </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O74" t="n">
+        <v>29</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.2922420812473295</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -17141,86 +17045,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG74" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN74" t="b">
-        <v>0</v>
-      </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -18422,7 +18268,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -18468,34 +18314,15 @@
       <c r="N80" t="n">
         <v>34</v>
       </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O80" t="n">
+        <v>34</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.3426286469796277</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -18503,86 +18330,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG80" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN80" t="b">
-        <v>0</v>
-      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -19784,7 +19553,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -19830,34 +19599,15 @@
       <c r="N86" t="n">
         <v>30</v>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O86" t="n">
+        <v>30</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.3023193943937891</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -19865,86 +19615,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG86" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN86" t="b">
-        <v>0</v>
-      </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -21146,7 +20838,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -21192,34 +20884,15 @@
       <c r="N92" t="n">
         <v>47</v>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O92" t="n">
+        <v>47</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.473633717883603</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -21227,86 +20900,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD92" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG92" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN92" t="b">
-        <v>0</v>
-      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ92" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -22735,7 +22350,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -22781,34 +22396,15 @@
       <c r="N99" t="n">
         <v>65</v>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O99" t="n">
+        <v>65</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.6550253545198765</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -22816,86 +22412,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD99" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE99" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF99" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG99" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN99" t="b">
-        <v>0</v>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -24097,7 +23635,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -24143,34 +23681,15 @@
       <c r="N105" t="n">
         <v>80</v>
       </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O105" t="n">
+        <v>80</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.806185051716771</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -24178,86 +23697,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD105" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE105" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN105" t="b">
-        <v>0</v>
-      </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -25686,7 +25147,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -25732,34 +25193,15 @@
       <c r="N112" t="n">
         <v>62</v>
       </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O112" t="n">
+        <v>62</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0.6247934150804976</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -25767,86 +25209,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>0</v>
-      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -27048,7 +26432,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -27094,34 +26478,15 @@
       <c r="N118" t="n">
         <v>87</v>
       </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O118" t="n">
+        <v>87</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.8767262437419885</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -27129,86 +26494,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>0</v>
-      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -28410,7 +27717,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -28456,34 +27763,15 @@
       <c r="N124" t="n">
         <v>69</v>
       </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X124" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O124" t="n">
+        <v>69</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.695334607105715</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -28491,86 +27779,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD124" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG124" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM124" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN124" t="b">
-        <v>0</v>
-      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -29999,7 +29229,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -30045,34 +29275,15 @@
       <c r="N131" t="n">
         <v>49</v>
       </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O131" t="n">
+        <v>49</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.4937883441765222</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -30080,86 +29291,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN131" t="b">
-        <v>0</v>
-      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -31361,7 +30514,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -31407,34 +30560,15 @@
       <c r="N137" t="n">
         <v>35</v>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O137" t="n">
+        <v>35</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.3527059601260873</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -31442,86 +30576,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN137" t="b">
-        <v>0</v>
-      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -32723,7 +31799,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -32769,34 +31845,15 @@
       <c r="N143" t="n">
         <v>42</v>
       </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O143" t="n">
+        <v>42</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.4175837975100373</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -32804,86 +31861,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN143" t="b">
-        <v>0</v>
-      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -34312,7 +33311,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -34358,34 +33357,15 @@
       <c r="N150" t="n">
         <v>15</v>
       </c>
-      <c r="U150" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O150" t="n">
+        <v>15</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0.149137070539299</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -34393,86 +33373,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD150" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE150" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG150" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN150" t="b">
-        <v>0</v>
-      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -35674,7 +34596,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -35720,34 +34642,15 @@
       <c r="N156" t="n">
         <v>25</v>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O156" t="n">
+        <v>25</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0.2485617842321651</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -35755,86 +34658,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>0</v>
-      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -37036,7 +35881,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -37082,34 +35927,15 @@
       <c r="N162" t="n">
         <v>36</v>
       </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O162" t="n">
+        <v>36</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.3579289692943177</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -37117,86 +35943,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>0</v>
-      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -38625,7 +37393,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -38671,34 +37439,15 @@
       <c r="N169" t="n">
         <v>38</v>
       </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V169" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W169" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y169" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O169" t="n">
+        <v>38</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0.3778139120328909</v>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -38706,86 +37455,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB169" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD169" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE169" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG169" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH169" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI169" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ169" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM169" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN169" t="b">
-        <v>0</v>
-      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -39987,7 +38678,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -40033,34 +38724,15 @@
       <c r="N175" t="n">
         <v>45</v>
       </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O175" t="n">
+        <v>45</v>
+      </c>
+      <c r="R175" t="n">
+        <v>0.4474112116178971</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -40068,86 +38740,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN175" t="b">
-        <v>0</v>
-      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -41349,7 +39963,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -41395,34 +40009,15 @@
       <c r="N181" t="n">
         <v>60</v>
       </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O181" t="n">
+        <v>60</v>
+      </c>
+      <c r="R181" t="n">
+        <v>0.5965482821571961</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -41430,86 +40025,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>0</v>
-      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -42938,7 +41475,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -42984,34 +41521,15 @@
       <c r="N188" t="n">
         <v>61</v>
       </c>
-      <c r="U188" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O188" t="n">
+        <v>61</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0.6064907535264827</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -43019,86 +41537,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD188" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE188" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF188" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG188" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH188" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI188" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ188" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN188" t="b">
-        <v>0</v>
-      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ188" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
@@ -44300,7 +42760,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -44346,34 +42806,15 @@
       <c r="N194" t="n">
         <v>68</v>
       </c>
-      <c r="U194" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O194" t="n">
+        <v>68</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0.676088053111489</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -44381,86 +42822,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>0</v>
-      </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ194" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
@@ -45662,7 +44045,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -45708,34 +44091,15 @@
       <c r="N200" t="n">
         <v>97</v>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O200" t="n">
+        <v>97</v>
+      </c>
+      <c r="R200" t="n">
+        <v>0.9644197228208005</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -45743,86 +44107,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD200" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE200" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG200" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH200" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI200" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM200" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN200" t="b">
-        <v>0</v>
-      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -47251,7 +45557,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -47297,34 +45603,15 @@
       <c r="N207" t="n">
         <v>67</v>
       </c>
-      <c r="U207" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V207" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y207" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O207" t="n">
+        <v>67</v>
+      </c>
+      <c r="R207" t="n">
+        <v>0.6661455817422024</v>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -47332,86 +45619,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB207" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD207" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE207" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ207" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM207" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN207" t="b">
-        <v>0</v>
-      </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ207" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -48613,7 +46842,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -48659,34 +46888,15 @@
       <c r="N213" t="n">
         <v>41</v>
       </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O213" t="n">
+        <v>41</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.4076413261407507</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -48694,86 +46904,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN213" t="b">
-        <v>0</v>
-      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -50202,7 +48354,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -50248,34 +48400,15 @@
       <c r="N220" t="n">
         <v>35</v>
       </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O220" t="n">
+        <v>35</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0.3439666698262462</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -50283,86 +48416,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE220" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF220" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG220" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN220" t="b">
-        <v>0</v>
-      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
@@ -51564,7 +49639,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -51610,34 +49685,15 @@
       <c r="N226" t="n">
         <v>31</v>
       </c>
-      <c r="U226" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V226" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W226" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X226" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y226" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O226" t="n">
+        <v>31</v>
+      </c>
+      <c r="R226" t="n">
+        <v>0.3046561932746752</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -51645,86 +49701,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB226" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD226" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE226" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF226" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG226" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH226" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI226" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ226" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK226" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM226" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN226" t="b">
-        <v>0</v>
-      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -52926,7 +50924,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -52972,34 +50970,15 @@
       <c r="N232" t="n">
         <v>41</v>
       </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V232" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W232" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X232" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y232" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O232" t="n">
+        <v>41</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0.4029323846536027</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -53007,86 +50986,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD232" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE232" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG232" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ232" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK232" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM232" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN232" t="b">
-        <v>0</v>
-      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
@@ -54288,7 +52209,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -54334,34 +52255,15 @@
       <c r="N238" t="n">
         <v>34</v>
       </c>
-      <c r="U238" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V238" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W238" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O238" t="n">
+        <v>34</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0.3341390506883535</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -54369,86 +52271,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD238" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE238" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG238" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH238" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI238" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ238" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK238" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM238" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN238" t="b">
-        <v>0</v>
-      </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ238" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
@@ -55877,7 +53721,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -55923,34 +53767,15 @@
       <c r="N245" t="n">
         <v>58</v>
       </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O245" t="n">
+        <v>58</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0.5700019099977794</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -55958,86 +53783,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN245" t="b">
-        <v>0</v>
-      </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ245" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
@@ -57239,7 +55006,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -57285,34 +55052,15 @@
       <c r="N251" t="n">
         <v>112</v>
       </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O251" t="n">
+        <v>112</v>
+      </c>
+      <c r="R251" t="n">
+        <v>1.100693343443988</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -57320,86 +55068,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>0</v>
-      </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ251" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
@@ -58601,7 +56291,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -58647,34 +56337,15 @@
       <c r="N257" t="n">
         <v>111</v>
       </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O257" t="n">
+        <v>111</v>
+      </c>
+      <c r="R257" t="n">
+        <v>1.090865724306095</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
@@ -58682,86 +56353,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN257" t="b">
-        <v>0</v>
-      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ257" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr"/>
       <c r="AT257" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
@@ -60190,7 +57803,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -60236,34 +57849,15 @@
       <c r="N264" t="n">
         <v>160</v>
       </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W264" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O264" t="n">
+        <v>160</v>
+      </c>
+      <c r="R264" t="n">
+        <v>1.57241906206284</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -60271,86 +57865,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD264" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG264" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH264" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ264" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK264" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM264" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN264" t="b">
-        <v>0</v>
-      </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
@@ -61552,7 +59088,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -61598,34 +59134,15 @@
       <c r="N270" t="n">
         <v>108</v>
       </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O270" t="n">
+        <v>108</v>
+      </c>
+      <c r="R270" t="n">
+        <v>1.061382866892417</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -61633,86 +59150,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN270" t="b">
-        <v>0</v>
-      </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
@@ -63141,7 +60600,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -63187,34 +60646,15 @@
       <c r="N277" t="n">
         <v>113</v>
       </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O277" t="n">
+        <v>113</v>
+      </c>
+      <c r="R277" t="n">
+        <v>1.110520962581881</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -63222,86 +60662,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD277" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE277" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG277" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ277" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK277" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN277" t="b">
-        <v>0</v>
-      </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ277" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS277" t="inlineStr"/>
       <c r="AT277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
@@ -64503,7 +61885,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -64549,34 +61931,15 @@
       <c r="N283" t="n">
         <v>66</v>
       </c>
-      <c r="U283" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V283" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W283" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X283" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y283" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z283" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O283" t="n">
+        <v>66</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0.6486228631009214</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -64584,86 +61947,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB283" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC283" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD283" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE283" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF283" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG283" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH283" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI283" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ283" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK283" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM283" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN283" t="b">
-        <v>0</v>
-      </c>
       <c r="AO283" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ283" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS283" t="inlineStr"/>
       <c r="AT283" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
@@ -65865,7 +63170,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -65911,34 +63216,15 @@
       <c r="N289" t="n">
         <v>56</v>
       </c>
-      <c r="U289" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V289" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W289" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X289" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y289" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O289" t="n">
+        <v>56</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0.550346671721994</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -65946,86 +63232,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC289" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD289" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE289" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF289" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG289" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH289" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI289" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ289" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK289" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM289" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN289" t="b">
-        <v>0</v>
-      </c>
       <c r="AO289" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ289" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS289" t="inlineStr"/>
       <c r="AT289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV289" t="inlineStr">
@@ -67454,7 +64682,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -67500,34 +64728,15 @@
       <c r="N296" t="n">
         <v>30</v>
       </c>
-      <c r="U296" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V296" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W296" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X296" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y296" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z296" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O296" t="n">
+        <v>30</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0.291853635401846</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -67535,86 +64744,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB296" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC296" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD296" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE296" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF296" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG296" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH296" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI296" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ296" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK296" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM296" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN296" t="b">
-        <v>0</v>
-      </c>
       <c r="AO296" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ296" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS296" t="inlineStr"/>
       <c r="AT296" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV296" t="inlineStr">
@@ -68816,7 +65967,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -68862,34 +66013,15 @@
       <c r="N302" t="n">
         <v>29</v>
       </c>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V302" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W302" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X302" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y302" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z302" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O302" t="n">
+        <v>29</v>
+      </c>
+      <c r="R302" t="n">
+        <v>0.2821251808884511</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -68897,86 +66029,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB302" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC302" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD302" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE302" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF302" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG302" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH302" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI302" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ302" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK302" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM302" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN302" t="b">
-        <v>0</v>
-      </c>
       <c r="AO302" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ302" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR302" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS302" t="inlineStr"/>
       <c r="AT302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV302" t="inlineStr">
@@ -70178,7 +67252,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -70224,34 +67298,15 @@
       <c r="N308" t="n">
         <v>29</v>
       </c>
-      <c r="U308" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V308" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W308" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X308" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y308" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O308" t="n">
+        <v>29</v>
+      </c>
+      <c r="R308" t="n">
+        <v>0.2821251808884511</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -70259,86 +67314,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB308" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC308" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD308" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE308" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF308" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG308" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH308" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI308" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ308" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK308" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM308" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN308" t="b">
-        <v>0</v>
-      </c>
       <c r="AO308" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP308" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ308" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR308" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS308" t="inlineStr"/>
       <c r="AT308" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV308" t="inlineStr">
@@ -71767,7 +68764,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -71813,34 +68810,15 @@
       <c r="N315" t="n">
         <v>29</v>
       </c>
-      <c r="U315" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W315" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X315" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y315" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O315" t="n">
+        <v>29</v>
+      </c>
+      <c r="R315" t="n">
+        <v>0.2821251808884511</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -71848,86 +68826,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB315" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC315" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD315" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE315" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF315" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG315" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ315" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK315" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM315" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN315" t="b">
-        <v>0</v>
-      </c>
       <c r="AO315" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP315" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ315" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS315" t="inlineStr"/>
       <c r="AT315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV315" t="inlineStr">
@@ -73129,7 +70049,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -73175,34 +70095,15 @@
       <c r="N321" t="n">
         <v>40</v>
       </c>
-      <c r="U321" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V321" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W321" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X321" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y321" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z321" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O321" t="n">
+        <v>40</v>
+      </c>
+      <c r="R321" t="n">
+        <v>0.3891381805357946</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -73210,86 +70111,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB321" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC321" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD321" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE321" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF321" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG321" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH321" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI321" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ321" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK321" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM321" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN321" t="b">
-        <v>0</v>
-      </c>
       <c r="AO321" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP321" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ321" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS321" t="inlineStr"/>
       <c r="AT321" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV321" t="inlineStr">
@@ -74491,7 +71334,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -74537,34 +71380,15 @@
       <c r="N327" t="n">
         <v>62</v>
       </c>
-      <c r="U327" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V327" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W327" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X327" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y327" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z327" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O327" t="n">
+        <v>62</v>
+      </c>
+      <c r="R327" t="n">
+        <v>0.6031641798304817</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -74572,86 +71396,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB327" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC327" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD327" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE327" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF327" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG327" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH327" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI327" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ327" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK327" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM327" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN327" t="b">
-        <v>0</v>
-      </c>
       <c r="AO327" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP327" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ327" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR327" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS327" t="inlineStr"/>
       <c r="AT327" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV327" t="inlineStr">
@@ -76080,7 +72846,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -76126,34 +72892,15 @@
       <c r="N334" t="n">
         <v>91</v>
       </c>
-      <c r="U334" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V334" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W334" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X334" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y334" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O334" t="n">
+        <v>91</v>
+      </c>
+      <c r="R334" t="n">
+        <v>0.8852893607189328</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -76161,86 +72908,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB334" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC334" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD334" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE334" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF334" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG334" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH334" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI334" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ334" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK334" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM334" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN334" t="b">
-        <v>0</v>
-      </c>
       <c r="AO334" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP334" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ334" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR334" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS334" t="inlineStr"/>
       <c r="AT334" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV334" t="inlineStr">
@@ -77442,7 +74131,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -77488,34 +74177,15 @@
       <c r="N340" t="n">
         <v>67</v>
       </c>
-      <c r="U340" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V340" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W340" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X340" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y340" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z340" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O340" t="n">
+        <v>67</v>
+      </c>
+      <c r="R340" t="n">
+        <v>0.651806452397456</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -77523,86 +74193,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB340" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC340" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD340" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE340" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF340" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG340" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH340" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI340" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ340" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK340" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM340" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN340" t="b">
-        <v>0</v>
-      </c>
       <c r="AO340" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP340" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ340" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR340" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS340" t="inlineStr"/>
       <c r="AT340" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU340" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV340" t="inlineStr">
@@ -78804,7 +75416,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -78850,34 +75462,15 @@
       <c r="N346" t="n">
         <v>82</v>
       </c>
-      <c r="U346" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V346" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W346" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X346" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y346" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z346" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O346" t="n">
+        <v>82</v>
+      </c>
+      <c r="R346" t="n">
+        <v>0.7977332700983789</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -78885,86 +75478,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB346" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC346" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD346" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE346" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF346" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG346" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH346" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI346" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ346" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK346" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM346" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN346" t="b">
-        <v>0</v>
-      </c>
       <c r="AO346" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP346" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ346" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR346" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS346" t="inlineStr"/>
       <c r="AT346" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU346" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV346" t="inlineStr">
@@ -80393,7 +76928,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -80439,34 +76974,15 @@
       <c r="N353" t="n">
         <v>71</v>
       </c>
-      <c r="U353" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V353" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W353" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X353" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y353" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z353" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O353" t="n">
+        <v>71</v>
+      </c>
+      <c r="R353" t="n">
+        <v>0.6907202704510355</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -80474,86 +76990,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB353" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC353" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD353" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE353" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF353" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG353" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH353" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI353" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ353" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK353" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM353" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN353" t="b">
-        <v>0</v>
-      </c>
       <c r="AO353" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP353" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ353" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR353" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS353" t="inlineStr"/>
       <c r="AT353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU353" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV353" t="inlineStr">
@@ -81755,7 +78213,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -81801,34 +78259,15 @@
       <c r="N359" t="n">
         <v>73</v>
       </c>
-      <c r="U359" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V359" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W359" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X359" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y359" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z359" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O359" t="n">
+        <v>73</v>
+      </c>
+      <c r="R359" t="n">
+        <v>0.7101771794778252</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -81836,86 +78275,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB359" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC359" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD359" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE359" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF359" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG359" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH359" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI359" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ359" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK359" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM359" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN359" t="b">
-        <v>0</v>
-      </c>
       <c r="AO359" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP359" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ359" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR359" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS359" t="inlineStr"/>
       <c r="AT359" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV359" t="inlineStr">
@@ -83117,7 +79498,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -83163,34 +79544,15 @@
       <c r="N365" t="n">
         <v>45</v>
       </c>
-      <c r="U365" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="V365" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_VME_TO_2020</t>
-        </is>
-      </c>
-      <c r="W365" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X365" t="inlineStr">
-        <is>
-          <t>Viral meningoencefalit</t>
-        </is>
-      </c>
-      <c r="Y365" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z365" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="O365" t="n">
+        <v>45</v>
+      </c>
+      <c r="R365" t="n">
+        <v>0.437780453102769</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -83198,86 +79560,28 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB365" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC365" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD365" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE365" t="inlineStr">
-        <is>
-          <t>aggregate</t>
-        </is>
-      </c>
-      <c r="AF365" t="inlineStr">
-        <is>
-          <t>not_comparable</t>
-        </is>
-      </c>
-      <c r="AG365" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI365" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ365" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_VME_including_TBE_to_2020</t>
-        </is>
-      </c>
-      <c r="AK365" t="inlineStr">
-        <is>
-          <t>Swedish viral meningoencephalitis aggregate through 2020, before TBE was excluded from this category.</t>
-        </is>
-      </c>
-      <c r="AM365" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN365" t="b">
-        <v>0</v>
-      </c>
       <c r="AO365" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ365" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS365" t="inlineStr"/>
       <c r="AT365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV365" t="inlineStr">
@@ -84572,7 +80876,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -84602,7 +80906,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>369</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -84612,7 +80916,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -84623,7 +80927,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
     </row>
@@ -84634,7 +80938,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="16">
